--- a/wooclap/imports/optional/07_Intro_ML_Part_1_optional.xlsx
+++ b/wooclap/imports/optional/07_Intro_ML_Part_1_optional.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$2</definedName>

--- a/wooclap/imports/optional/07_Intro_ML_Part_1_optional.xlsx
+++ b/wooclap/imports/optional/07_Intro_ML_Part_1_optional.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L03-O01 · A training collection has a few labeled photos and many unlabeled photos. Learning from both is called what?</t>
+          <t>L03-O01 · A system learns from labeled scans at hospital A and unlabeled scans at hospital B. B uses a different scanner. Which interpretation is justified?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -527,22 +527,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Semi-supervised learning.</t>
+          <t>Using both pools can be semi-supervised learning, while the scanner difference introduces domain shift.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Testing only.</t>
+          <t>Semi-supervised learning guarantees that both hospitals have the same input distribution.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Reinforcement learning because every photo gives a reward.</t>
+          <t>A scanner difference by itself proves the training labels are noisy.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Supervised learning that ignores all unlabeled photos.</t>
+          <t>Adding unlabeled B scans automatically corrects every scanner-related performance difference.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
